--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vishw\Documents\GitHub\OrangeHRMProject\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73668274-B201-414B-B8BC-CB1F75551CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="validLogin" sheetId="1" r:id="rId1"/>
+    <sheet name="invalidLogin" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>Username</t>
   </si>
@@ -40,8 +40,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -54,7 +54,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -67,13 +66,7 @@
     </fill>
   </fills>
   <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color auto="1"/>
@@ -87,7 +80,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -104,14 +96,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -120,10 +104,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -255,6 +239,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -278,10 +263,11 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -290,13 +276,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -372,6 +358,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -391,21 +378,19 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -413,7 +398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -421,15 +406,30 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>